--- a/docs/Quản trị dự án CNTT.xlsx
+++ b/docs/Quản trị dự án CNTT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPU\ky7\Script-Blockchain\Game_BlockChain-NodeJs-\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4CC6C6E8-42BE-4DA8-B512-9785074D4D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE1D010-4455-4048-A71F-F15E468F7129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{317657C2-F133-4AA6-87F4-E327DC189DE0}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Man-month" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -240,229 +240,229 @@
     <t>Hạng mục chi phí</t>
   </si>
   <si>
-    <t>Diễn giải (Căn cứ)</t>
-  </si>
-  <si>
-    <t>Thành tiền (đơn vị VNĐ)</t>
-  </si>
-  <si>
-    <t>I.</t>
-  </si>
-  <si>
     <t>Chi phí nhân sự</t>
   </si>
   <si>
-    <t>Cập nhật theo WBS thực tế: man-month mỗi vị trí = tổng giờ vị trí / 176. Thành tiền = man-month x lương trung bình vị trí, làm tròn lên 100,000 VNĐ.</t>
-  </si>
-  <si>
     <t>Nhân sự - Automation Engineer</t>
   </si>
   <si>
-    <t>23.5 giờ (~0.13 MM) x 35,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Backend</t>
   </si>
   <si>
-    <t>15.5 giờ (~0.09 MM) x 30,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Backend Architect</t>
   </si>
   <si>
-    <t>51.5 giờ (~0.29 MM) x 65,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Backend Engineer</t>
   </si>
   <si>
-    <t>24 giờ (~0.14 MM) x 35,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Backend Lead</t>
   </si>
   <si>
-    <t>47 giờ (~0.27 MM) x 52,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Backend Team</t>
   </si>
   <si>
-    <t>152.5 giờ (~0.87 MM) x 35,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Blockchain Engineer</t>
   </si>
   <si>
     <t>Nhân sự - Data Architect</t>
   </si>
   <si>
-    <t>31 giờ (~0.18 MM) x 60,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - DB Engineer</t>
   </si>
   <si>
-    <t>63 giờ (~0.36 MM) x 40,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - DevOps</t>
   </si>
   <si>
-    <t>99.5 giờ (~0.57 MM) x 40,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Frontend</t>
   </si>
   <si>
-    <t>22 giờ (~0.12 MM) x 30,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Frontend Lead</t>
   </si>
   <si>
-    <t>31 giờ (~0.18 MM) x 47,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Infra</t>
   </si>
   <si>
-    <t>15.5 giờ (~0.09 MM) x 35,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Ops</t>
   </si>
   <si>
-    <t>8 giờ (~0.05 MM) x 26,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Performance Engineer</t>
   </si>
   <si>
-    <t>31 giờ (~0.18 MM) x 39,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - PM</t>
   </si>
   <si>
-    <t>23.5 giờ (~0.13 MM) x 47,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Product Owner</t>
   </si>
   <si>
-    <t>8 giờ (~0.05 MM) x 45,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - QA</t>
   </si>
   <si>
-    <t>33.5 giờ (~0.19 MM) x 26,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - QA Lead</t>
   </si>
   <si>
-    <t>27.5 giờ (~0.16 MM) x 40,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Realtime Engineer</t>
   </si>
   <si>
-    <t>43 giờ (~0.24 MM) x 40,000,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Security Engineer</t>
   </si>
   <si>
-    <t>39 giờ (~0.22 MM) x 47,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
-    <t>Nhân sự - SRE</t>
-  </si>
-  <si>
-    <t>19.5 giờ (~0.11 MM) x 47,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
     <t>Nhân sự - Tech Lead</t>
   </si>
   <si>
-    <t>61 giờ (~0.35 MM) x 57,500,000 VNĐ/tháng. Lý do: phân bổ giờ trực tiếp từ các task có assignee chứa vị trí này trong WBS.</t>
-  </si>
-  <si>
-    <t>II.</t>
-  </si>
-  <si>
     <t>Chi phí hạ tầng và công nghệ</t>
   </si>
   <si>
-    <t>Ước tính theo kiến trúc microservices + blockchain của dự án, làm tròn lên 100,000 VNĐ.</t>
-  </si>
-  <si>
     <t>Cloud compute cho microservices</t>
   </si>
   <si>
-    <t>Triển khai nhiều service Node.js, socket game và môi trường dev/test/staging cần compute ổn định.</t>
-  </si>
-  <si>
-    <t>Managed database (MySQL/PostgreSQL)</t>
-  </si>
-  <si>
-    <t>Lưu trữ dữ liệu nghiệp vụ (user/inventory/market/trade), cần backup và khả năng phục hồi.</t>
-  </si>
-  <si>
     <t>Blockchain node/RPC &amp; contract ops</t>
   </si>
   <si>
-    <t>Vận hành RPC và tác vụ triển khai/kiểm thử smart contract cho blockchain-service.</t>
-  </si>
-  <si>
     <t>Object storage + CDN</t>
   </si>
   <si>
-    <t>Lưu trữ tệp upload/static và tối ưu truy cập từ client.</t>
-  </si>
-  <si>
     <t>CI/CD, registry, monitoring/logging</t>
   </si>
   <si>
-    <t>Tự động build/deploy, lưu artifact/image và theo dõi lỗi, hiệu năng.</t>
-  </si>
-  <si>
     <t>Domain, SSL, email/SMS/API ngoài</t>
   </si>
   <si>
-    <t>Tên miền, bảo mật SSL và dịch vụ tích hợp bên thứ ba phục vụ xác thực/thông báo.</t>
-  </si>
-  <si>
-    <t>III.</t>
-  </si>
-  <si>
     <t>Chi phí quản lý &amp; vận hành</t>
   </si>
   <si>
-    <t>Gồm dự phòng rủi ro và chi phí vận hành phục vụ phát hành/bàn giao.</t>
-  </si>
-  <si>
     <t>Dự phòng rủi ro (Contingency)</t>
   </si>
   <si>
-    <t>10% của (I + II), để hấp thụ biến động tích hợp và phát sinh kỹ thuật.</t>
-  </si>
-  <si>
-    <t>Chi phí vận hành nội bộ và bản quyền phần mềm</t>
-  </si>
-  <si>
-    <t>Các khoản phục vụ quản trị dự án, cộng tác và vận hành trong giai đoạn thực thi.</t>
-  </si>
-  <si>
     <t>Release hardening &amp; handover</t>
   </si>
   <si>
-    <t>Chuẩn bị phát hành, hoàn thiện tài liệu vận hành và hỗ trợ chuyển giao.</t>
-  </si>
-  <si>
-    <t>TỔNG CỘNG (I+II+III)</t>
+    <t>Diễn giải (Căn cứ cập nhật từ file CSV WBS)</t>
+  </si>
+  <si>
+    <t>Thành tiền (VNĐ)</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>278 giờ (~1.58 MM) × 47,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>301 giờ (~1.71 MM) × 57,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>4 giờ (~0.02 MM) × 45,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>48.5 giờ (~0.28 MM) × 40,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>27.5 giờ (~0.16 MM) × 65,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>16 giờ (~0.09 MM) × 60,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>8 giờ (~0.05 MM) × 30,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>8 giờ (~0.05 MM) × 35,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>25 giờ (~0.14 MM) × 52,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>22.5 giờ (~0.13 MM) × 40,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>87 giờ (~0.49 MM) × 35,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>41 giờ (~0.23 MM) × 40,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>13 giờ (~0.07 MM) × 35,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>16 giờ (~0.09 MM) × 47,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>11.5 giờ (~0.07 MM) × 30,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>20.5 giờ (~0.12 MM) × 26,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>20 giờ (~0.11 MM) × 47,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>Nhân sự - SRE/DevOps</t>
+  </si>
+  <si>
+    <t>20 giờ (~0.11 MM) × 43,750,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>18 giờ (~0.10 MM) × 40,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>15.5 giờ (~0.09 MM) × 35,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>20 giờ (~0.11 MM) × 39,000,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>5 giờ (~0.03 MM) × 26,500,000 VNĐ/tháng</t>
+  </si>
+  <si>
+    <t>II</t>
+  </si>
+  <si>
+    <t>Giữ nguyên theo kiến trúc microservices + blockchain của dự án</t>
+  </si>
+  <si>
+    <t>Triển khai service Node.js, socket realtime, môi trường dev/test/staging</t>
+  </si>
+  <si>
+    <t>Managed database</t>
+  </si>
+  <si>
+    <t>MySQL/PostgreSQL backup &amp; recovery</t>
+  </si>
+  <si>
+    <t>RPC, deploy và test smart contract</t>
+  </si>
+  <si>
+    <t>Lưu trữ static/upload và tối ưu truy cập</t>
+  </si>
+  <si>
+    <t>Build/deploy tự động và giám sát hệ thống</t>
+  </si>
+  <si>
+    <t>Dịch vụ tích hợp và bảo mật</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Cập nhật theo tổng mới của I + II</t>
+  </si>
+  <si>
+    <t>10% của (I + II)</t>
+  </si>
+  <si>
+    <t>Chi phí vận hành nội bộ &amp; bản quyền</t>
+  </si>
+  <si>
+    <t>Công cụ quản trị và cộng tác dự án</t>
+  </si>
+  <si>
+    <t>Chuẩn bị phát hành và bàn giao</t>
+  </si>
+  <si>
+    <t>TỔNG CỘNG (I + II + III)</t>
+  </si>
+  <si>
+    <t>Tính lại theo tổng giờ công trong file NEW WBS.csv. Man-month = tổng giờ / 176. Thành tiền = MM × lương trung bình vị trí, làm tròn lên 100,000 VNĐ.</t>
   </si>
 </sst>
 </file>
@@ -981,7 +981,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -999,6 +999,33 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1403,9 +1430,8 @@
       <c r="E2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7">
-        <f>SUM(F3:F4)</f>
-        <v>28</v>
+      <c r="F2" s="8">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1424,8 +1450,8 @@
       <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6">
-        <v>16</v>
+      <c r="F3" s="9">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1444,8 +1470,8 @@
       <c r="E4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="6">
-        <v>12</v>
+      <c r="F4" s="9">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" s="1" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1464,9 +1490,8 @@
       <c r="E5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="7">
-        <f>SUM(F6:F7)</f>
-        <v>71</v>
+      <c r="F5" s="8">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1485,8 +1510,8 @@
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="6">
-        <v>24</v>
+      <c r="F6" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1505,8 +1530,8 @@
       <c r="E7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="6">
-        <v>47</v>
+      <c r="F7" s="9">
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="1" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1525,9 +1550,8 @@
       <c r="E8" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="7">
-        <f>SUM(F9:F10)</f>
-        <v>62</v>
+      <c r="F8" s="8">
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1546,8 +1570,8 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="6">
-        <v>31</v>
+      <c r="F9" s="9">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1566,8 +1590,8 @@
       <c r="E10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="6">
-        <v>31</v>
+      <c r="F10" s="9">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1586,9 +1610,8 @@
       <c r="E11" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="7">
-        <f>SUM(F12:F26)</f>
-        <v>576</v>
+      <c r="F11" s="8">
+        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1607,8 +1630,8 @@
       <c r="E12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="6">
-        <v>47</v>
+      <c r="F12" s="9">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1627,8 +1650,8 @@
       <c r="E13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F13" s="6">
-        <v>31</v>
+      <c r="F13" s="9">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1647,8 +1670,8 @@
       <c r="E14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="6">
-        <v>39</v>
+      <c r="F14" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1667,8 +1690,8 @@
       <c r="E15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="6">
-        <v>55</v>
+      <c r="F15" s="9">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1687,8 +1710,8 @@
       <c r="E16" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="6">
-        <v>47</v>
+      <c r="F16" s="9">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1707,8 +1730,8 @@
       <c r="E17" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="6">
-        <v>31</v>
+      <c r="F17" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1727,8 +1750,8 @@
       <c r="E18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F18" s="6">
-        <v>63</v>
+      <c r="F18" s="9">
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1747,8 +1770,8 @@
       <c r="E19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="6">
-        <v>55</v>
+      <c r="F19" s="9">
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1767,8 +1790,8 @@
       <c r="E20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="6">
-        <v>24</v>
+      <c r="F20" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1787,8 +1810,8 @@
       <c r="E21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="6">
-        <v>31</v>
+      <c r="F21" s="9">
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1807,8 +1830,8 @@
       <c r="E22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="6">
-        <v>24</v>
+      <c r="F22" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1827,8 +1850,8 @@
       <c r="E23" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="6">
-        <v>20</v>
+      <c r="F23" s="9">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1847,8 +1870,8 @@
       <c r="E24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="6">
-        <v>39</v>
+      <c r="F24" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1867,8 +1890,8 @@
       <c r="E25" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F25" s="6">
-        <v>39</v>
+      <c r="F25" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1887,8 +1910,8 @@
       <c r="E26" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F26" s="6">
-        <v>31</v>
+      <c r="F26" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6" s="1" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
@@ -1907,9 +1930,8 @@
       <c r="E27" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F27" s="7">
-        <f>SUM(F28:F32)</f>
-        <v>180</v>
+      <c r="F27" s="8">
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1928,8 +1950,8 @@
       <c r="E28" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="6">
-        <v>55</v>
+      <c r="F28" s="9">
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1948,8 +1970,8 @@
       <c r="E29" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="6">
-        <v>47</v>
+      <c r="F29" s="9">
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1968,8 +1990,8 @@
       <c r="E30" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="6">
-        <v>31</v>
+      <c r="F30" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -1988,8 +2010,8 @@
       <c r="E31" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="6">
-        <v>31</v>
+      <c r="F31" s="9">
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -2008,8 +2030,8 @@
       <c r="E32" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F32" s="6">
-        <v>16</v>
+      <c r="F32" s="9">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -2020,9 +2042,9 @@
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
-      <c r="F33" s="6">
+      <c r="F33" s="7">
         <f>SUM(F2,F5,F8,F11,F27)</f>
-        <v>917</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -2067,15 +2089,15 @@
         <v>0</v>
       </c>
       <c r="C2" s="4">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4">
         <f>C2/8</f>
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="E2" s="4">
         <f>ROUND(C2/176,2)</f>
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -2086,15 +2108,15 @@
         <v>62</v>
       </c>
       <c r="C3" s="4">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" ref="D3:D6" si="0">C3/8</f>
-        <v>8.875</v>
+        <v>5.875</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" ref="E3:E6" si="1">ROUND(C3/176,2)</f>
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -2105,15 +2127,15 @@
         <v>11</v>
       </c>
       <c r="C4" s="4">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>7.75</v>
+        <v>5.125</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" si="1"/>
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -2124,15 +2146,15 @@
         <v>17</v>
       </c>
       <c r="C5" s="4">
-        <v>576</v>
+        <v>301</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>37.625</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" si="1"/>
-        <v>3.27</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -2143,15 +2165,15 @@
         <v>46</v>
       </c>
       <c r="C6" s="4">
-        <v>180</v>
+        <v>118</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v>22.5</v>
+        <v>14.75</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" si="1"/>
-        <v>1.02</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -2161,15 +2183,15 @@
       <c r="B7" s="5"/>
       <c r="C7" s="3">
         <f>SUM(C2:C6)</f>
-        <v>917</v>
+        <v>525</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(D2:D6)</f>
-        <v>114.625</v>
+        <v>65.625</v>
       </c>
       <c r="E7" s="3">
         <f>SUM(E2:E6)</f>
-        <v>5.1999999999999993</v>
+        <v>2.98</v>
       </c>
     </row>
   </sheetData>
@@ -2191,515 +2213,517 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C2" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="13">
+        <v>286400000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="14">
+        <v>75100000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="14">
+        <v>98400000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="16">
+        <v>1.3</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="14">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="16">
+        <v>1.4</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="14">
+        <v>11100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="16">
+        <v>1.5</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="14">
+        <v>10200000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="16">
+        <v>1.6</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="14">
+        <v>5500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="16">
+        <v>1.7</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="16">
+        <v>1.8</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="14">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="16">
+        <v>1.9</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D11" s="14">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="16">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="14">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="16">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="14">
+        <v>17400000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="16">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="D14" s="14">
+        <v>7500000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="16">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="14">
+        <v>9400000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="16">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2600000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="16">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="14">
+        <v>4400000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="16">
+        <v>1.17</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="14">
+        <v>3100000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="16">
+        <v>1.18</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="14">
+        <v>5400000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="16">
+        <v>1.19</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="14">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="14">
+        <v>4100000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="16">
+        <v>1.21</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="7">
-        <v>227600000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="6">
-        <v>4600000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="6">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6">
-        <v>1.3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="6">
-        <v>18900000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D6" s="6">
+      <c r="C23" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="14">
+        <v>3100000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="16">
+        <v>1.22</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="14">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="16">
+        <v>1.23</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="14">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" s="13">
+        <v>48000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="16">
+        <v>2.1</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" s="14">
+        <v>18000000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="16">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="14">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="16">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D29" s="14">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="16">
+        <v>2.4</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="14">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="16">
+        <v>2.5</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D31" s="14">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="16">
+        <v>2.6</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" s="14">
         <v>5000000</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="6">
-        <v>14200000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
-        <v>1.6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="6">
-        <v>30500000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="6">
-        <v>14200000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="6">
-        <v>10800000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="6">
-        <v>14400000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="6">
-        <v>22800000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="6">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="6">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" s="6">
-        <v>8600000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="6" t="s">
+    <row r="33" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="6">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="C33" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="D33" s="13">
+        <v>43500000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="B34" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C34" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="14">
+        <v>33500000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D35" s="14">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="16">
+        <v>3.3</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="6">
-        <v>1400000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="6">
-        <v>7100000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="6">
-        <v>6200000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2300000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="6">
-        <v>5100000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="6">
-        <v>1.19</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="6">
-        <v>6400000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="6">
-        <v>9600000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6">
-        <v>1.21</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D23" s="6">
-        <v>10500000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D24" s="6">
-        <v>5300000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D25" s="6">
-        <v>20200000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="7">
-        <v>48000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6">
-        <v>2.1</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D27" s="6">
-        <v>18000000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="6">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="6">
-        <v>8000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="6">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C36" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="14">
         <v>4000000</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="D31" s="6">
-        <v>7000000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="6">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" s="7" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" s="7">
-        <v>37600000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="D34" s="6">
-        <v>27600000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="6">
-        <v>6000000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C36" s="6" t="s">
+    <row r="37" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="12"/>
+      <c r="B37" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="6">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="45.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="6">
-        <v>313200000</v>
+      <c r="C37" s="12"/>
+      <c r="D37" s="13">
+        <v>377900000</v>
       </c>
     </row>
   </sheetData>
